--- a/healthcare_forms/007_eligibility_quiz--healthcare_forms.xlsx
+++ b/healthcare_forms/007_eligibility_quiz--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eligibility_questions</t>
+          <t>eligibility_question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eligibility Questions</t>
+          <t>Is this person 18 years or older?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_1</t>
+          <t>eligibility_question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Is this person 18 years or older?</t>
+          <t>Has this person been previously diagnosed with any of the following medical conditions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2</t>
+          <t>eligibility_question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Has this person been previously diagnosed with any of the following medical conditions?</t>
+          <t>How many hours do you sleep each night?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_3</t>
+          <t>eligibility_question_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Has this person received any vaccinations or immunizations?</t>
+          <t>Do you have access to internet?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_4</t>
+          <t>eligibility_question_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How many years ago was the last time this person smoked?</t>
+          <t>Do you have a stable job or income?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_5</t>
+          <t>eligibility_question_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Has this person ever used any of the following substances?</t>
+          <t>Do you have a stable residence address?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_6</t>
+          <t>eligibility_question_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is this person's weight in kilograms?</t>
+          <t>Has this person ever used any of the following substances?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_7</t>
+          <t>eligibility_question_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is this person's height in centimeters?</t>
+          <t>What is this person's weight in kilograms?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_8</t>
+          <t>eligibility_question_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is this person's BMI?</t>
+          <t>What is this person's height in centimeters?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9</t>
+          <t>eligibility_question_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Has this person ever experienced any of the following medical conditions?</t>
+          <t>What is this person's BMI?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_10</t>
+          <t>eligibility_question_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Has this person been previously diagnosed with any of the following medical conditions?</t>
+          <t>Do you have a history of smoking?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,361 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_11</t>
+          <t>eligibility_question_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Are you able to perform physical activity?</t>
+          <t>Do you take any medications?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Do you take any medications?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How many hours do you spend watching TV or using electronic media each day?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How many hours do you sleep each night?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Do you have a stable job or income?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Do you have a stable residence address?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Do you have access to internet?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Is this person 18 years or older?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Has this person been previously diagnosed with any of the following medical conditions?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Has this person received any vaccinations or immunizations?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How many years ago was the last time this person smoked?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Has this person ever used any of the following substances?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is this person's weight in kilograms?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is this person's height in centimeters?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>What is this person's BMI?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Has this person ever experienced any of the following medical conditions?</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1144,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1172,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_1_choices</t>
+          <t>eligibility_question_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1189,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_1_choices</t>
+          <t>eligibility_question_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1206,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1223,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1240,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1257,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1274,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1291,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_2_choices</t>
+          <t>eligibility_question_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1308,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_5_choices</t>
+          <t>eligibility_question_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1325,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_5_choices</t>
+          <t>eligibility_question_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1342,646 +997,170 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hypertension</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chronic_kidney_disease</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Heart Disease</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chronic_liver_disease</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chronic Liver Disease</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_9_choices</t>
+          <t>eligibility_question_7_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>respiratory_disease</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Respiratory Disease</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_10_choices</t>
+          <t>eligibility_question_11_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hypertension</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_10_choices</t>
+          <t>eligibility_question_11_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Diabetes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_10_choices</t>
+          <t>eligibility_question_12_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>chronic_kidney_disease</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chronic Kidney Disease</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>eligibility_quiz_questions_10_choices</t>
+          <t>eligibility_question_12_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>heart_disease</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heart Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_10_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>chronic_liver_disease</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chronic Liver Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_10_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>respiratory_disease</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Respiratory Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_11_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_11_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_12_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_12_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_15_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_15_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_16_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_16_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_17_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_17_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_18_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>18_years_or_older</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>18 years or older</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_18_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>less_than_18_years</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>less than 18 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>hypertension</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Hypertension</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>diabetes</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Diabetes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>chronic_kidney_disease</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Chronic Kidney Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>heart_disease</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Heart Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>chronic_liver_disease</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Chronic Liver Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_19_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>respiratory_disease</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Respiratory Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_22_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_22_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>hypertension</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Hypertension</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>diabetes</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Diabetes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>chronic_kidney_disease</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Chronic Kidney Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>heart_disease</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Heart Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>chronic_liver_disease</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chronic Liver Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>eligibility_quiz_questions_26_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>respiratory_disease</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Respiratory Disease</t>
         </is>
       </c>
     </row>
